--- a/artfynd/A 50388-2022 artfynd.xlsx
+++ b/artfynd/A 50388-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50388-2022 artfynd.xlsx
+++ b/artfynd/A 50388-2022 artfynd.xlsx
@@ -2290,12 +2290,7 @@
         <v>104535259</v>
       </c>
       <c r="B16" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,16 +2316,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603895.3223768467</v>
+        <v>603895</v>
       </c>
       <c r="R16" t="n">
-        <v>6461056.904809761</v>
+        <v>6461057</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,27 +2363,18 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50388-2022 artfynd.xlsx
+++ b/artfynd/A 50388-2022 artfynd.xlsx
@@ -2290,7 +2290,7 @@
         <v>104535259</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50388-2022 artfynd.xlsx
+++ b/artfynd/A 50388-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2153574</v>
+        <v>95496</v>
       </c>
       <c r="B2" t="n">
-        <v>77531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>93</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ekpricklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Inoderma byssaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Weigel) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603815.3039912595</v>
+        <v>603815</v>
       </c>
       <c r="R2" t="n">
-        <v>6460772.256920712</v>
+        <v>6460769</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,53 +777,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>177084</v>
+        <v>104520997</v>
       </c>
       <c r="B3" t="n">
-        <v>78839</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FLATMOSSEN, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603815.3039912595</v>
+        <v>603844</v>
       </c>
       <c r="R3" t="n">
-        <v>6460772.256920712</v>
+        <v>6460569</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,73 +860,64 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95496</v>
+        <v>104521105</v>
       </c>
       <c r="B4" t="n">
-        <v>73520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekpricklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inoderma byssaceum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Weigel) Gray</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>FLATMOSSEN, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603815.38692027</v>
+        <v>603858</v>
       </c>
       <c r="R4" t="n">
-        <v>6460769.102076584</v>
+        <v>6460536</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +941,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,35 +958,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104520593</v>
+        <v>104535297</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,38 +984,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603824.7630602617</v>
+        <v>603833</v>
       </c>
       <c r="R5" t="n">
-        <v>6460833.540885269</v>
+        <v>6461036</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,19 +1041,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,70 +1058,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104520634</v>
+        <v>104535290</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603817.0348268487</v>
+        <v>603700</v>
       </c>
       <c r="R6" t="n">
-        <v>6460746.519981585</v>
+        <v>6460836</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,19 +1138,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,56 +1155,47 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Torbjörn Blixt</t>
+          <t>Marika Sjödin, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104520800</v>
+        <v>104520485</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1301,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603859.667650962</v>
+        <v>603880</v>
       </c>
       <c r="R7" t="n">
-        <v>6460608.728488009</v>
+        <v>6461053</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,19 +1236,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,15 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104519694</v>
+        <v>104535236</v>
       </c>
       <c r="B8" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,38 +1276,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603760.4564287175</v>
+        <v>603854</v>
       </c>
       <c r="R8" t="n">
-        <v>6460853.423426609</v>
+        <v>6461059</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,19 +1333,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,66 +1350,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104520557</v>
+        <v>104535237</v>
       </c>
       <c r="B9" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Okänt, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603885.3556372428</v>
+        <v>603864</v>
       </c>
       <c r="R9" t="n">
-        <v>6461055.064205693</v>
+        <v>6461031</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,19 +1430,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,56 +1447,47 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Marika Sjödin, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104520645</v>
+        <v>104521096</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1644,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603816.0902450657</v>
+        <v>603856</v>
       </c>
       <c r="R10" t="n">
-        <v>6460722.291079731</v>
+        <v>6460536</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1677,19 +1528,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,51 +1550,42 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Torbjörn Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104519364</v>
+        <v>104519061</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1761,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603770.079593877</v>
+        <v>603661</v>
       </c>
       <c r="R11" t="n">
-        <v>6460727.922205786</v>
+        <v>6460880</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1794,19 +1626,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,44 +1655,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104519331</v>
+        <v>104519694</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1878,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603772.2972907786</v>
+        <v>603761</v>
       </c>
       <c r="R12" t="n">
-        <v>6460723.771065069</v>
+        <v>6460853</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1911,19 +1724,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,51 +1753,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104520485</v>
+        <v>104520557</v>
       </c>
       <c r="B13" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Okänt, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603880.1434658376</v>
+        <v>603885</v>
       </c>
       <c r="R13" t="n">
-        <v>6461052.822559929</v>
+        <v>6461055</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2024,19 +1822,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,60 +1844,56 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104535290</v>
+        <v>104520593</v>
       </c>
       <c r="B14" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603699.7645825362</v>
+        <v>603825</v>
       </c>
       <c r="R14" t="n">
-        <v>6460836.044529563</v>
+        <v>6460833</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,19 +1920,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,27 +1937,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Torbjörn Blixt</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104535297</v>
+        <v>104535259</v>
       </c>
       <c r="B15" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,34 +1960,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603833.1645451345</v>
+        <v>603895</v>
       </c>
       <c r="R15" t="n">
-        <v>6461035.276872259</v>
+        <v>6461057</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2248,27 +2025,18 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2287,56 +2055,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104535259</v>
+        <v>104519331</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603895</v>
+        <v>603772</v>
       </c>
       <c r="R16" t="n">
-        <v>6461057</v>
+        <v>6460724</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2374,72 +2139,71 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104535236</v>
+        <v>104519364</v>
       </c>
       <c r="B17" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603854.1668077807</v>
+        <v>603770</v>
       </c>
       <c r="R17" t="n">
-        <v>6461058.452922393</v>
+        <v>6460728</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2466,19 +2230,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,65 +2247,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Torbjörn Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104535237</v>
+        <v>104520634</v>
       </c>
       <c r="B18" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603863.3276843964</v>
+        <v>603817</v>
       </c>
       <c r="R18" t="n">
-        <v>6461030.808710222</v>
+        <v>6460746</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2578,19 +2332,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,65 +2349,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Torbjörn Blixt</t>
+          <t>Eva Siljeholm, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104535285</v>
+        <v>104520645</v>
       </c>
       <c r="B19" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603678.6934493788</v>
+        <v>603817</v>
       </c>
       <c r="R19" t="n">
-        <v>6460835.491308701</v>
+        <v>6460722</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2690,19 +2434,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,65 +2451,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Torbjörn Blixt</t>
+          <t>Eva Siljeholm, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104535300</v>
+        <v>104520800</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603789.4701153082</v>
+        <v>603859</v>
       </c>
       <c r="R20" t="n">
-        <v>6461013.082770315</v>
+        <v>6460609</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2802,19 +2536,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,62 +2553,61 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104535299</v>
+        <v>104535271</v>
       </c>
       <c r="B21" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603760.1568332873</v>
+        <v>603834</v>
       </c>
       <c r="R21" t="n">
-        <v>6461065.452072009</v>
+        <v>6461035</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2914,27 +2637,18 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2946,57 +2660,56 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104535301</v>
+        <v>104535272</v>
       </c>
       <c r="B22" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603779.6362570875</v>
+        <v>603884</v>
       </c>
       <c r="R22" t="n">
-        <v>6460946.004204682</v>
+        <v>6461057</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3026,27 +2739,18 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3058,22 +2762,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104535272</v>
+        <v>104535278</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +2799,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>113</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3109,10 +2808,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>603884.2468143021</v>
+        <v>603830</v>
       </c>
       <c r="R23" t="n">
-        <v>6461057.13957022</v>
+        <v>6461036</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3142,19 +2841,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,61 +2864,52 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Torbjörn Blixt</t>
+          <t>Marika Sjödin, Olle Jonsson, Eva Siljeholm, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104535278</v>
+        <v>104535285</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>603830.5031378204</v>
+        <v>603679</v>
       </c>
       <c r="R24" t="n">
-        <v>6461036.259167619</v>
+        <v>6460836</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3259,28 +2939,17 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3292,64 +2961,56 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Olle Jonsson, Eva Siljeholm, Torbjörn Blixt</t>
+          <t>Marika Sjödin, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104535271</v>
+        <v>104520864</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>603834.2456976952</v>
+        <v>603808</v>
       </c>
       <c r="R25" t="n">
-        <v>6461034.253027688</v>
+        <v>6460599</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3376,43 +3037,421 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104521024</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Söderköping, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>603847</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6460540</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104535299</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ängelholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>603760</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6461066</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Marika Sjödin, Eva Siljeholm, Torbjörn Blixt</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104535300</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ängelholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>603790</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6461013</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>104535301</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ängelholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>603779</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6460946</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50388-2022 artfynd.xlsx
+++ b/artfynd/A 50388-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95496</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520997</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104521105</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535297</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1164,6 +1189,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535290</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520485</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535236</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535237</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104521096</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104519061</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104519694</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520557</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520593</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2052,6 +2122,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535259</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104519331</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2256,6 +2336,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104519364</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2358,6 +2443,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520634</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2460,6 +2550,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520645</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2562,6 +2657,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520800</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2664,6 +2764,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535271</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2766,6 +2871,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535272</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2868,6 +2978,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535278</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2965,6 +3080,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535285</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3063,6 +3183,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520864</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,6 +3286,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104521024</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3258,6 +3388,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535299</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3355,6 +3490,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535300</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3452,8 +3592,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535301</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>